--- a/data/current/392927406_2025-12-11T09_37_00Z.xlsx
+++ b/data/current/392927406_2025-12-11T09_37_00Z.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11207"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD2EAF2-6E57-2A4D-97EA-8AB2A081B842}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="9560" yWindow="5140" windowWidth="20360" windowHeight="9840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Объявления" sheetId="1" r:id="rId1"/>
@@ -14,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="76">
   <si>
     <t>ContactPhone</t>
   </si>
@@ -112,9 +113,6 @@
     <t>EMail</t>
   </si>
   <si>
-    <t>rubble_13.01_5</t>
-  </si>
-  <si>
     <t>Намик</t>
   </si>
   <si>
@@ -220,9 +218,6 @@
     <t>Карьерный</t>
   </si>
   <si>
-    <t>simple-sand_17.03_15</t>
-  </si>
-  <si>
     <t>7243036587</t>
   </si>
   <si>
@@ -242,13 +237,19 @@
   </si>
   <si>
     <t>380</t>
+  </si>
+  <si>
+    <t>r00-4070_cheh_031225_01</t>
+  </si>
+  <si>
+    <t>s00_dmd_031225_01</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -283,12 +284,20 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -544,11 +553,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AF3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="45" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>28</v>
       </c>
@@ -646,190 +658,191 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" t="s">
+        <v>60</v>
+      </c>
+      <c r="M2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O2" t="s">
         <v>32</v>
       </c>
-      <c r="B2" t="s">
+      <c r="P2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>40</v>
+      </c>
+      <c r="R2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" t="s">
+        <v>57</v>
+      </c>
+      <c r="T2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U2" t="s">
+        <v>48</v>
+      </c>
+      <c r="V2" t="s">
+        <v>53</v>
+      </c>
+      <c r="X2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF2" t="s">
         <v>34</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J3" t="s">
+        <v>68</v>
+      </c>
+      <c r="K3" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" t="s">
+        <v>73</v>
+      </c>
+      <c r="M3" t="s">
+        <v>71</v>
+      </c>
+      <c r="N3" t="s">
+        <v>69</v>
+      </c>
+      <c r="O3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>63</v>
+      </c>
+      <c r="R3" t="s">
+        <v>38</v>
+      </c>
+      <c r="S3" t="s">
         <v>57</v>
       </c>
-      <c r="D2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="T3" t="s">
+        <v>47</v>
+      </c>
+      <c r="U3" t="s">
+        <v>66</v>
+      </c>
+      <c r="V3" t="s">
+        <v>72</v>
+      </c>
+      <c r="W3" t="s">
+        <v>70</v>
+      </c>
+      <c r="X3" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD3" t="s">
         <v>51</v>
       </c>
-      <c r="G2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L2" t="s">
-        <v>61</v>
-      </c>
-      <c r="M2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N2" t="s">
-        <v>45</v>
-      </c>
-      <c r="O2" t="s">
-        <v>33</v>
-      </c>
-      <c r="P2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>41</v>
-      </c>
-      <c r="R2" t="s">
-        <v>39</v>
-      </c>
-      <c r="S2" t="s">
-        <v>58</v>
-      </c>
-      <c r="T2" t="s">
-        <v>48</v>
-      </c>
-      <c r="U2" t="s">
-        <v>49</v>
-      </c>
-      <c r="V2" t="s">
-        <v>54</v>
-      </c>
-      <c r="X2" t="s">
-        <v>60</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>59</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>38</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" t="s">
-        <v>51</v>
-      </c>
-      <c r="G3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I3" t="s">
-        <v>63</v>
-      </c>
-      <c r="J3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K3" t="s">
-        <v>44</v>
-      </c>
-      <c r="L3" t="s">
-        <v>75</v>
-      </c>
-      <c r="M3" t="s">
-        <v>73</v>
-      </c>
-      <c r="N3" t="s">
-        <v>71</v>
-      </c>
-      <c r="O3" t="s">
-        <v>33</v>
-      </c>
-      <c r="P3" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>64</v>
-      </c>
-      <c r="R3" t="s">
-        <v>39</v>
-      </c>
-      <c r="S3" t="s">
-        <v>58</v>
-      </c>
-      <c r="T3" t="s">
-        <v>48</v>
-      </c>
-      <c r="U3" t="s">
-        <v>67</v>
-      </c>
-      <c r="V3" t="s">
-        <v>74</v>
-      </c>
-      <c r="W3" t="s">
-        <v>72</v>
-      </c>
-      <c r="X3" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>62</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>59</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>52</v>
-      </c>
       <c r="AF3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>